--- a/resources/tools/wordlist_E-J/lessons/lesson-13.xlsx
+++ b/resources/tools/wordlist_E-J/lessons/lesson-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B142"/>
+  <dimension ref="A1:B147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,240 +431,240 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>waiter</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ウエイター</t>
+          <t>大人|おとな</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>(someone's) house/home</t>
+          <t>lawyer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>お宅|おたく</t>
+          <t>弁護士|べんごし</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>I (formal)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>大人|おとな</t>
+          <t>私|わたくし</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>foreign language</t>
+          <t>curry</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>外国語|がいこくご</t>
+          <t>カレー</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>musical instrument</t>
+          <t>black tea</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>楽器|がっき</t>
+          <t>紅茶|こうちゃ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>karate</t>
+          <t>kimono; Japanese traditional dress</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>空手|からて</t>
+          <t>着物|きもの</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>curry</t>
+          <t>sweater</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>カレー</t>
+          <t>セーター</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kimono; Japanese traditional dress</t>
+          <t>musical instrument</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>着物|きもの</t>
+          <t>楽器|がっき</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>advertisement</t>
+          <t>karate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>広告|こうこく</t>
+          <t>空手|からて</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tea (black tea)</t>
+          <t>golf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>紅茶|こうちゃ</t>
+          <t>ゴルフ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>言葉|ことば</t>
+          <t>バイク</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>golf</t>
+          <t>elephant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ゴルフ</t>
+          <t>象|ぞう</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sweater</t>
+          <t>body</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>セーター</t>
+          <t>体|からだ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>elephant</t>
+          <t>foreign language</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>象|ぞう</t>
+          <t>外国語|がいこくご</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>violin</t>
+          <t>language</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>バイオリン</t>
+          <t>言葉|ことば</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>grammar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>バイク</t>
+          <t>文法|ぶんぽう</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>(consumer) prices</t>
+          <t>application</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>物価|ぶっか</t>
+          <t>アプリ</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>grammar</t>
+          <t>apartment; smaller apartment building</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>文法|ぶんぽう</t>
+          <t>アパート</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>lawyer</t>
+          <t>larger apartment building; condominium</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>弁護士|べんごし</t>
+          <t>マンション</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>recruitment</t>
+          <t>airport</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>募集|ぼしゅう</t>
+          <t>空港|くうこう</t>
         </is>
       </c>
     </row>
@@ -683,48 +683,48 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>yakuza; gangster</t>
+          <t>(consumer) prices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>やくざ</t>
+          <t>物価|ぶっか</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>promise; appointment</t>
+          <t>advertisement</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>約束|やくそく</t>
+          <t>広告|こうこく</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>(term) paper</t>
+          <t>recruitment</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>レポート</t>
+          <t>募集|ぼしゅう</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>I (formal)</t>
+          <t>promise; appointment</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>私|わたくし</t>
+          <t>約束|やくそく</t>
         </is>
       </c>
     </row>
@@ -755,108 +755,108 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hot and spicy; salty</t>
+          <t>strict</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>辛い|からい</t>
+          <t>厳しい|きびしい</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>strict</t>
+          <t>to feel sick</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>厳しい|きびしい</t>
+          <t>気分が悪い|きぶんがわるい</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>incredible; awesome</t>
+          <t>hot and spicy; salty</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>すごい</t>
+          <t>辛い|からい</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>close; near</t>
+          <t>incredible; awesome</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>近い|ちかい</t>
+          <t>すごい</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>various; different kinds of</t>
+          <t>close; near</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>いろいろ（な）</t>
+          <t>近い|ちかい</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>happy (lasting happiness)</t>
+          <t>various; different kinds of</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>幸せ|しあわせ（な）</t>
+          <t>いろいろ（な）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>no good</t>
+          <t>happy (lasting happiness)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>だめ（な）</t>
+          <t>幸せ|しあわせ（な）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>to knit</t>
+          <t>no good</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>編む|あむ</t>
+          <t>だめ（な）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>to lend; to rent</t>
+          <t>to knit (～を)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>貸す|かす</t>
+          <t>編む|あむ</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>to brush (teeth); to polish</t>
+          <t>to brush (teeth); to polish (～を)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>to be moved/touched (by...)</t>
+          <t>to be moved/touched (by...) (～に)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -923,288 +923,288 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>someone honorable is present/home</t>
+          <t>...times</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>いらっしゃいませ</t>
+          <t>～回|～かい</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>...times</t>
+          <t>...kilometers; ...kilograms</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>～回|～かい</t>
+          <t>～キロ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>...kilometers; ...kilograms</t>
+          <t>all</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>～キロ</t>
+          <t>全部|ぜんぶ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>as a matter of fact,...</t>
+          <t>my name is...</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>実は|じつは</t>
+          <t>～と申します|～ともうします</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>especially</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>全部|ぜんぶ</t>
+          <t>特に|とくに</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>my name is...</t>
+          <t>one day</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>～と申します|～ともうします</t>
+          <t>一日|いちにち</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>one day</t>
+          <t>two days</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>一日|いちにち</t>
+          <t>二日|ふつか</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>two days</t>
+          <t>three days</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>二日|ふつか</t>
+          <t>三日|みっか</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>three days</t>
+          <t>four days</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>三日|みっか</t>
+          <t>四日|よっか</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>four days</t>
+          <t>five days</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>四日|よっか</t>
+          <t>五日|いつか</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>five days</t>
+          <t>six days</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>五日|いつか</t>
+          <t>六日|むいか</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>six days</t>
+          <t>seven days</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>六日|むいか</t>
+          <t>七日|なのか</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>seven days</t>
+          <t>eight days</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>七日|なのか</t>
+          <t>八日|ようか</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>eight days</t>
+          <t>nine days</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>八日|ようか</t>
+          <t>九日|ここのか</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nine days</t>
+          <t>ten days</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>九日|ここのか</t>
+          <t>十日|とおか</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ten days</t>
+          <t>account</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>十日|とおか</t>
+          <t>口座|こうざ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>account</t>
+          <t>commission</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>口座|こうざ</t>
+          <t>手数料|てすうりょう</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>commission</t>
+          <t>bank card</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>手数料|てすうりょう</t>
+          <t>キャッシュカード</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bank card</t>
+          <t>passbook</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>キャッシュカード</t>
+          <t>通帳|つうちょう</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>passbook</t>
+          <t>savings</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>通帳|つうちょう</t>
+          <t>預金|よきん</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>savings</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>預金|よきん</t>
+          <t>金額|きんがく</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>100-yen coin</t>
+          <t>personal identification number</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>百円玉|ひゃくえんだま</t>
+          <t>暗証番号|あんしょうばんごう</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>金額|きんがく</t>
+          <t>現金|げんきん</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>personal identification number</t>
+          <t>money exchange</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>暗証番号|あんしょうばんごう</t>
+          <t>両替|りょうがえ</t>
         </is>
       </c>
     </row>
@@ -1415,655 +1415,655 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bird</t>
+          <t>commodity prices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>鳥|とり</t>
+          <t>物価|ぶっか</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>grilled chicken</t>
+          <t>bird</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>焼き鳥|やきとり</t>
+          <t>鳥|とり</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>swan</t>
+          <t>grilled chicken</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>白鳥|はくちょう</t>
+          <t>焼き鳥|やきとり</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>cooking</t>
+          <t>swan</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>料理|りょうり</t>
+          <t>白鳥|はくちょう</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>charge</t>
+          <t>cooking</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>料金|りょうきん</t>
+          <t>料理|りょうり</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tuition</t>
+          <t>charge</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>授業料|じゅぎょうりょう</t>
+          <t>料金|りょうきん</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>salary</t>
+          <t>tuition</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>給料|きゅうりょう</t>
+          <t>授業料|じゅぎょうりょう</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>cooking</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>料理|りょうり</t>
+          <t>給料|きゅうりょう</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>cooking</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>理由|りゆう</t>
+          <t>料理|りょうり</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>geography</t>
+          <t>reason</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>地理|ちり</t>
+          <t>理由|りゆう</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>geography</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>無理な|むりな</t>
+          <t>地理|ちり</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>especially</t>
+          <t>impossible</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>特に|とくに</t>
+          <t>無理な|むりな</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>special</t>
+          <t>especially</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>特別な|とくべつな</t>
+          <t>特に|とくに</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>characteristic</t>
+          <t>special</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>特徴|とくちょう</t>
+          <t>特別な|とくべつな</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>super express</t>
+          <t>characteristic</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>特急|とっきゅう</t>
+          <t>特徴|とくちょう</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>cheap</t>
+          <t>super express</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>安い|やすい</t>
+          <t>特急|とっきゅう</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>safe</t>
+          <t>cheap</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>安全な|あんぜんな</t>
+          <t>安い|やすい</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>relief</t>
+          <t>safe</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>安心|あんしん</t>
+          <t>安全な|あんぜんな</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>uneasy</t>
+          <t>relief</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>不安な|ふあんな</t>
+          <t>安心|あんしん</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>rice; meal</t>
+          <t>anxious; worried</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ご飯|ごはん</t>
+          <t>不安な|ふあんな</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>breakfast</t>
+          <t>rice; meal</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>朝ご飯|あさごはん</t>
+          <t>ご飯|ごはん</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>dinner</t>
+          <t>breakfast</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>晩ご飯|ばんごはん</t>
+          <t>朝ご飯|あさごはん</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>meat</t>
+          <t>lunch</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>肉|にく</t>
+          <t>昼ご飯|ひるごはん</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>beef</t>
+          <t>dinner</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>牛肉|ぎゅうにく</t>
+          <t>晩ご飯|ばんごはん</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>pork</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>豚肉|ぶたにく</t>
+          <t>肉|にく</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>meat shop</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>肉屋|にくや</t>
+          <t>牛肉|ぎゅうにく</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>muscle</t>
+          <t>pork</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>筋肉|きんにく</t>
+          <t>豚肉|ぶたにく</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>meat shop</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>悪い|わるい</t>
+          <t>肉屋|にくや</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>to feel sick</t>
+          <t>muscle</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>気分が悪い|きぶんがわるい</t>
+          <t>筋肉|きんにく</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>the worst</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>最悪|さいあく</t>
+          <t>悪い|わるい</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>devil</t>
+          <t>to feel sick</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>悪魔|あくま</t>
+          <t>気分が悪い|きぶんがわるい</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>body</t>
+          <t>the worst</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>体|からだ</t>
+          <t>最悪|さいあく</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>body weight</t>
+          <t>devil</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>体重|たいじゅう</t>
+          <t>悪魔|あくま</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>gymnastics; physical exercises</t>
+          <t>body</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>体操|たいそう</t>
+          <t>体|からだ</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>airport</t>
+          <t>body weight</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>空港|くうこう</t>
+          <t>体重|たいじゅう</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>air</t>
+          <t>gymnastics; physical exercises</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>空気|くうき</t>
+          <t>体操|たいそう</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>sky</t>
+          <t>the same</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>空|そら</t>
+          <t>同じ|おなじ</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>to be vacant</t>
+          <t>coworker</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>空く|あく</t>
+          <t>同僚|どうりょう</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>karate</t>
+          <t>classmate</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>空手|からて</t>
+          <t>同級生|どうきゅうせい</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kobe Port</t>
+          <t>same time</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>神戸港|こうべこう</t>
+          <t>同時|どうじ</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>to arrive</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>港|みなと</t>
+          <t>着く|つく</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>to wear</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>香港|ほんこん</t>
+          <t>着る|きる</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>to arrive</t>
+          <t>kimono</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>着く|つく</t>
+          <t>着物|きもの</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>to wear</t>
+          <t>swimwear</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>着る|きる</t>
+          <t>水着|みずぎ</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kimono</t>
+          <t>arriving at Osaka</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>着物|きもの</t>
+          <t>大阪着|おおさかちゃく</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>arriving at Osaka</t>
+          <t>airport</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>大阪着|おおさかちゃく</t>
+          <t>空港|くうこう</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>the same</t>
+          <t>air</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>同じ|おなじ</t>
+          <t>空気|くうき</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>coworker</t>
+          <t>sky</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>同僚|どうりょう</t>
+          <t>空|そら</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>classmate</t>
+          <t>to be vacant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>同級生|どうきゅうせい</t>
+          <t>空く|あく</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>same time</t>
+          <t>karate</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>同時|どうじ</t>
+          <t>空手|からて</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>sea</t>
+          <t>airport</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>海|うみ</t>
+          <t>空港|くうこう</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>the Japan Sea</t>
+          <t>Kobe Port</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>日本海|にほんかい</t>
+          <t>神戸港|こうべこう</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>overseas</t>
+          <t>port</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>海外|かいがい</t>
+          <t>港|みなと</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>coast</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>海岸|かいがん</t>
+          <t>香港|ほんこん</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>noon</t>
+          <t>noon; daytime</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2117,6 +2117,66 @@
       <c r="B142" t="inlineStr">
         <is>
           <t>昼食|ちゅうしょく</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>海|うみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>the Japan Sea</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>日本海|にほんかい</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>overseas</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>海外|かいがい</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>coast</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>海岸|かいがん</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Hokkaido</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>北海道|ほっかいどう</t>
         </is>
       </c>
     </row>
